--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488253_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488253_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9882</v>
+        <v>3.3069</v>
       </c>
       <c r="E2" t="n">
-        <v>5.337</v>
+        <v>2.6065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6512</v>
+        <v>0.7004</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0064</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8093</v>
+        <v>2.128</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5502</v>
+        <v>1.8196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2591</v>
+        <v>0.3084</v>
       </c>
       <c r="V2" t="n">
         <v>1.2589</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>L. LÓPEZ CALZADA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.951</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8779</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0731</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1902</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4027</v>
+        <v>0.3221</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5929</v>
+        <v>0.6221</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4022</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5884</v>
+        <v>0.3221</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9906</v>
+        <v>0.6221</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.212</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1857</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3977</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8349</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7292</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. LÓPEZ CALZADA</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.6916</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3221</v>
+        <v>0.2826</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6221</v>
+        <v>-0.2841</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.0215</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3221</v>
+        <v>0.0215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.2841</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -766,28 +766,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0631</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.0432</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0199</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6675</v>
+        <v>0.6309</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0332</v>
+        <v>0.8779</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7007</v>
+        <v>-0.247</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0015</v>
+        <v>0.1902</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2826</v>
+        <v>-0.4027</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2841</v>
+        <v>0.5929</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0215</v>
+        <v>1.4022</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0215</v>
+        <v>-0.5884</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9906</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.023</v>
+        <v>-1.212</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2611</v>
+        <v>0.1857</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2841</v>
+        <v>-1.3977</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.039</v>
+        <v>0.5148</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0547</v>
+        <v>0.1057</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.4091</v>
       </c>
       <c r="V5" t="n">
-        <v>0.63</v>
+        <v>-0.63</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X5" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9581</v>
+        <v>-0.5951</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9815</v>
+        <v>1.2518</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0234</v>
+        <v>-1.8468</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0311</v>
+        <v>1.467</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3167</v>
+        <v>3.1952</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2856</v>
+        <v>-1.7282</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2625</v>
+        <v>4.7034</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8418</v>
+        <v>4.0279</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5793</v>
+        <v>0.6755</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2314</v>
+        <v>-3.2364</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5251</v>
+        <v>-0.8327</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-2.4037</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.0763</v>
+        <v>-2.594</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.5586</v>
+        <v>-3.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1443</v>
+        <v>0.217</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7423999999999999</v>
+        <v>-0.0603</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4019</v>
+        <v>0.2773</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9428</v>
+        <v>0.315</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5722</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3269</v>
+        <v>-1.0691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0677</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3945</v>
+        <v>-1.1483</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3526</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5434</v>
+        <v>0.8011</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6367</v>
+        <v>0.6482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.1529</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8883</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6796</v>
+        <v>-1.174</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4642</v>
+        <v>-4.0254</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7846</v>
+        <v>2.8515</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2931</v>
+        <v>-2.813</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3208</v>
+        <v>-2.8192</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9724</v>
+        <v>0.0062</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8609</v>
+        <v>-3.9596</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3952</v>
+        <v>-2.7061</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4657</v>
+        <v>-1.2536</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4322</v>
+        <v>1.1466</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9255</v>
+        <v>-0.1131</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5067</v>
+        <v>1.2597</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6676</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.631</v>
+        <v>0.7508</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3967</v>
+        <v>0.5282</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2343</v>
+        <v>0.2226</v>
       </c>
       <c r="V9" t="n">
-        <v>0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X9" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9245</v>
+        <v>-1.2738</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2178</v>
+        <v>-1.7309</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1423</v>
+        <v>0.4571</v>
       </c>
       <c r="G10" t="n">
-        <v>1.467</v>
+        <v>0.0311</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1952</v>
+        <v>1.3167</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7282</v>
+        <v>-1.2856</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7034</v>
+        <v>1.2625</v>
       </c>
       <c r="K10" t="n">
-        <v>4.0279</v>
+        <v>1.8418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6755</v>
+        <v>-0.5793</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2364</v>
+        <v>-1.2314</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8327</v>
+        <v>-0.5251</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4037</v>
+        <v>-0.7063</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.594</v>
+        <v>-4.0763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7057</v>
+        <v>-5.5586</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1125</v>
+        <v>1.8286</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0943</v>
+        <v>0.993</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0182</v>
+        <v>0.8356</v>
       </c>
       <c r="V10" t="n">
-        <v>0.315</v>
+        <v>0.9428</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>1.5722</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0005</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2107</v>
+        <v>-1.423</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5698</v>
+        <v>-2.2568</v>
       </c>
       <c r="F11" t="n">
-        <v>2.359</v>
+        <v>0.8338</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.813</v>
+        <v>-4.2931</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8192</v>
+        <v>-1.3208</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0062</v>
+        <v>-2.9724</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9596</v>
+        <v>-2.8609</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7061</v>
+        <v>-0.3952</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2536</v>
+        <v>-2.4657</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1466</v>
+        <v>-1.4322</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1131</v>
+        <v>-0.9255</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2597</v>
+        <v>-0.5067</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.286</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0161</v>
+        <v>0.6041</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2699</v>
+        <v>0.2835</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.9535</v>
+        <v>-9.9939</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0354</v>
+        <v>-5.9034</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9181</v>
+        <v>-4.0905</v>
       </c>
       <c r="G12" t="n">
         <v>-6.7729</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2542</v>
+        <v>0.7054</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9637</v>
+        <v>0.1682</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7095</v>
+        <v>0.5372</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8883</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.1804</v>
+        <v>-9.6333</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.317500000000001</v>
+        <v>-7.770200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8629</v>
+        <v>-1.862899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-12.285</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1472</v>
+        <v>-2.147200000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-10.1377</v>
@@ -1456,10 +1456,10 @@
         <v>-6.6877</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.952</v>
+        <v>-4.952000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.5586</v>
+        <v>-5.558599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.7493</v>
@@ -1468,13 +1468,13 @@
         <v>10.1908</v>
       </c>
       <c r="S13" t="n">
-        <v>7.3492</v>
+        <v>7.8964</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3029</v>
+        <v>4.8499</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0464</v>
+        <v>3.0465</v>
       </c>
       <c r="V13" t="n">
         <v>0.3139999999999996</v>
@@ -1483,7 +1483,7 @@
         <v>3.7744</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.460500000000001</v>
+        <v>-3.4605</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2933</v>
+        <v>6.3445</v>
       </c>
       <c r="E14" t="n">
-        <v>4.715</v>
+        <v>4.0295</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5783</v>
+        <v>2.3149</v>
       </c>
       <c r="G14" t="n">
         <v>6.9565</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1875</v>
+        <v>-0.7614</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3719</v>
+        <v>-0.3137</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1843</v>
+        <v>-0.4477</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8888</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5577</v>
+        <v>4.2526</v>
       </c>
       <c r="E15" t="n">
         <v>1.9668</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5909</v>
+        <v>2.2858</v>
       </c>
       <c r="G15" t="n">
         <v>4.147</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.349</v>
+        <v>-0.6541</v>
       </c>
       <c r="T15" t="n">
         <v>-0.332</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.017</v>
+        <v>-0.3221</v>
       </c>
       <c r="V15" t="n">
         <v>0.945</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5766</v>
+        <v>3.5681</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5127</v>
+        <v>3.3168</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0639</v>
+        <v>0.2512</v>
       </c>
       <c r="G16" t="n">
         <v>1.1242</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0813</v>
+        <v>0.0727</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1567</v>
+        <v>-0.0391</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1119</v>
       </c>
       <c r="V16" t="n">
         <v>1.2594</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8235</v>
+        <v>2.4379</v>
       </c>
       <c r="E17" t="n">
-        <v>0.544</v>
+        <v>0.7398</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2795</v>
+        <v>1.6981</v>
       </c>
       <c r="G17" t="n">
         <v>2.1871</v>
@@ -1780,13 +1780,13 @@
         <v>2.4087</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.458</v>
+        <v>-1.8435</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0943</v>
+        <v>-0.8984</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3637</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3144</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7806999999999999</v>
+        <v>1.1799</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0646</v>
+        <v>-2.6728</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8453</v>
+        <v>3.8527</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1785</v>
@@ -1858,13 +1858,13 @@
         <v>2.7793</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1901</v>
+        <v>-0.7909</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.378</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4204</v>
+        <v>-0.4129</v>
       </c>
       <c r="V18" t="n">
         <v>-0.63</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5461</v>
+        <v>-0.0221</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8024</v>
+        <v>-0.7045</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2563</v>
+        <v>0.6823</v>
       </c>
       <c r="G19" t="n">
         <v>0.5664</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.483</v>
+        <v>-0.9591</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4414</v>
+        <v>-0.3435</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0416</v>
+        <v>-0.6156</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5066</v>
+        <v>-0.9585</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1986</v>
+        <v>-2.0028</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6921</v>
+        <v>1.0442</v>
       </c>
       <c r="G20" t="n">
         <v>0.068</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0187</v>
+        <v>-0.4707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3867</v>
+        <v>-0.1909</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.632</v>
+        <v>-0.2798</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0252</v>
+        <v>-1.5264</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.707</v>
+        <v>-0.5111</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3182</v>
+        <v>-1.0153</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0895</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.824</v>
+        <v>-0.3252</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>-0.3513</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2768</v>
+        <v>0.0261</v>
       </c>
       <c r="V21" t="n">
         <v>0.6294</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7737</v>
+        <v>-3.7897</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1031</v>
+        <v>-2.2989</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6706</v>
+        <v>-1.4908</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4962</v>
@@ -2170,13 +2170,13 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2955</v>
+        <v>-0.3115</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0037</v>
+        <v>-0.1996</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2917</v>
+        <v>-0.1119</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.1802</v>
+        <v>11.4863</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8628</v>
+        <v>1.862800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>8.317499999999999</v>
+        <v>9.623100000000001</v>
       </c>
       <c r="G23" t="n">
         <v>12.285</v>
@@ -2248,13 +2248,13 @@
         <v>15.7494</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.349499999999999</v>
+        <v>-6.0437</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0463</v>
+        <v>-3.0465</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.302899999999999</v>
+        <v>-2.9971</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3138000000000001</v>
